--- a/data/shePERMITS - License Tracker.xlsx
+++ b/data/shePERMITS - License Tracker.xlsx
@@ -37,7 +37,7 @@
     <t>NC</t>
   </si>
   <si>
-    <t>Commercial Building, Higway</t>
+    <t>Commercial Building, Highway</t>
   </si>
   <si>
     <t>Active</t>
@@ -46,7 +46,7 @@
     <t xml:space="preserve">Cape Fear Development Group, Inc. </t>
   </si>
   <si>
-    <t>Commercial Building Higway</t>
+    <t>Commercial Building Highway</t>
   </si>
   <si>
     <t xml:space="preserve">SC </t>
@@ -149,10 +149,10 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
@@ -418,13 +418,13 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="2">
         <v>74948.0</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="4">
         <v>46387.0</v>
       </c>
       <c r="F2" s="1" t="s">
@@ -439,13 +439,13 @@
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="2">
         <v>41228.0</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="4">
         <v>46387.0</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -466,7 +466,7 @@
       <c r="D4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="4">
         <v>46326.0</v>
       </c>
       <c r="F4" s="1" t="s">

--- a/data/shePERMITS - License Tracker.xlsx
+++ b/data/shePERMITS - License Tracker.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="29">
   <si>
     <t>Company Name</t>
   </si>
@@ -46,9 +46,6 @@
     <t xml:space="preserve">Cape Fear Development Group, Inc. </t>
   </si>
   <si>
-    <t>Commercial Building Highway</t>
-  </si>
-  <si>
     <t xml:space="preserve">SC </t>
   </si>
   <si>
@@ -67,7 +64,7 @@
     <t>AL</t>
   </si>
   <si>
-    <t>Buidling Construction, Highways &amp; Streets</t>
+    <t>Building Construction, Highways &amp; Streets</t>
   </si>
   <si>
     <t>LA</t>
@@ -149,10 +146,10 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
@@ -418,13 +415,13 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="2">
         <v>74948.0</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="3">
         <v>46387.0</v>
       </c>
       <c r="F2" s="1" t="s">
@@ -439,13 +436,13 @@
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>11</v>
+      <c r="C3" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D3" s="2">
         <v>41228.0</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="3">
         <v>46387.0</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -458,15 +455,15 @@
         <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="4">
+      <c r="E4" s="3">
         <v>46326.0</v>
       </c>
       <c r="F4" s="1" t="s">
@@ -479,15 +476,15 @@
         <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>16</v>
       </c>
       <c r="D5" s="2">
         <v>76469.0</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="3">
         <v>46812.0</v>
       </c>
       <c r="F5" s="1" t="s">
@@ -500,10 +497,10 @@
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="D6" s="2">
         <v>58053.0</v>
@@ -521,10 +518,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="D7" s="2">
         <v>72533.0</v>
@@ -542,13 +539,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="E8" s="7">
         <v>46424.0</v>
@@ -563,13 +560,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="E9" s="7">
         <v>46205.0</v>
@@ -584,10 +581,10 @@
         <v>6</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D10" s="2">
         <v>18871.0</v>
@@ -596,7 +593,7 @@
         <v>46010.0</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G10" s="1"/>
     </row>
@@ -605,13 +602,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="E11" s="8">
         <v>46265.0</v>
